--- a/exports/trend_1d/SIEMENS_full_report.xlsx
+++ b/exports/trend_1d/SIEMENS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.99</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42110</v>
+        <v>42111</v>
       </c>
       <c r="H2" t="n">
-        <v>1069.85</v>
+        <v>1010</v>
       </c>
       <c r="I2" t="n">
         <v>1013.21048003621</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K2" t="n">
-        <v>48.51</v>
+        <v>40.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.77</v>
@@ -555,7 +578,7 @@
         <v>1.24</v>
       </c>
       <c r="N2" t="n">
-        <v>4.52</v>
+        <v>5.59</v>
       </c>
       <c r="O2" t="n">
         <v>1.5</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>13.9</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42187</v>
+        <v>42188</v>
       </c>
       <c r="H3" t="n">
-        <v>1076.3</v>
+        <v>1088.1</v>
       </c>
       <c r="I3" t="n">
         <v>1081.571622141241</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.56</v>
+        <v>-7.73</v>
       </c>
       <c r="L3" t="n">
-        <v>7.26</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>3.8</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H4" t="n">
-        <v>1097.75</v>
+        <v>1054.5</v>
       </c>
       <c r="I4" t="n">
         <v>1063.250667085156</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>0.89</v>
+        <v>-3.09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>3.62</v>
       </c>
       <c r="M4" t="n">
         <v>1.21</v>
       </c>
       <c r="N4" t="n">
-        <v>2.43</v>
+        <v>3.94</v>
       </c>
       <c r="O4" t="n">
         <v>1.1</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>10.09</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42221</v>
+        <v>42222</v>
       </c>
       <c r="H5" t="n">
-        <v>1140.6</v>
+        <v>1162.5</v>
       </c>
       <c r="I5" t="n">
         <v>1142.417794108598</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.17</v>
+        <v>-10.24</v>
       </c>
       <c r="L5" t="n">
-        <v>9.01</v>
+        <v>12.68</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="N5" t="n">
         <v>5.07</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.52</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H6" t="n">
-        <v>1094.5</v>
+        <v>1070.75</v>
       </c>
       <c r="I6" t="n">
         <v>1075.08572758802</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.85</v>
+        <v>-7.89</v>
       </c>
       <c r="L6" t="n">
-        <v>6.14</v>
+        <v>8.19</v>
       </c>
       <c r="M6" t="n">
         <v>0.29</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.38</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42278</v>
+        <v>42282</v>
       </c>
       <c r="H7" t="n">
-        <v>1023.8</v>
+        <v>1040.65</v>
       </c>
       <c r="I7" t="n">
         <v>1026.635008123087</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K7" t="n">
-        <v>4.38</v>
+        <v>2.81</v>
       </c>
       <c r="L7" t="n">
         <v>4.87</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>10.12</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42312</v>
+        <v>42313</v>
       </c>
       <c r="H8" t="n">
-        <v>992.55</v>
+        <v>969.8</v>
       </c>
       <c r="I8" t="n">
         <v>978.7850658864569</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.62</v>
+        <v>-6.81</v>
       </c>
       <c r="L8" t="n">
-        <v>5.54</v>
+        <v>7.21</v>
       </c>
       <c r="M8" t="n">
         <v>0.47</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.13</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42460</v>
+        <v>42461</v>
       </c>
       <c r="H9" t="n">
-        <v>837.75</v>
+        <v>855.45</v>
       </c>
       <c r="I9" t="n">
         <v>842.8017443233974</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K9" t="n">
-        <v>13.62</v>
+        <v>11.79</v>
       </c>
       <c r="L9" t="n">
         <v>2.9</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42584</v>
+        <v>42585</v>
       </c>
       <c r="H10" t="n">
-        <v>975.55</v>
+        <v>948.75</v>
       </c>
       <c r="I10" t="n">
         <v>961.4505883803407</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K10" t="n">
-        <v>14.04</v>
+        <v>10.91</v>
       </c>
       <c r="L10" t="n">
         <v>2.85</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42740</v>
+        <v>42741</v>
       </c>
       <c r="H11" t="n">
-        <v>869.7</v>
+        <v>886.85</v>
       </c>
       <c r="I11" t="n">
         <v>871.7031352592744</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K11" t="n">
-        <v>8.33</v>
+        <v>6.52</v>
       </c>
       <c r="L11" t="n">
         <v>6.8</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.11</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H12" t="n">
-        <v>1035.6</v>
+        <v>1014.55</v>
       </c>
       <c r="I12" t="n">
         <v>1025.145473198437</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K12" t="n">
-        <v>16.77</v>
+        <v>14.4</v>
       </c>
       <c r="L12" t="n">
         <v>2.66</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42942</v>
+        <v>42943</v>
       </c>
       <c r="H13" t="n">
-        <v>1055.2</v>
+        <v>1059.3</v>
       </c>
       <c r="I13" t="n">
         <v>1057.631399219634</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.01</v>
+        <v>-4.41</v>
       </c>
       <c r="L13" t="n">
         <v>5.27</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.31</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42955</v>
+        <v>42956</v>
       </c>
       <c r="H14" t="n">
-        <v>1024.2</v>
+        <v>1009.95</v>
       </c>
       <c r="I14" t="n">
         <v>1020.310582913397</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.31</v>
+        <v>-4.66</v>
       </c>
       <c r="L14" t="n">
-        <v>4.21</v>
+        <v>5.32</v>
       </c>
       <c r="M14" t="n">
         <v>3.42</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42991</v>
+        <v>42992</v>
       </c>
       <c r="H15" t="n">
-        <v>1017.25</v>
+        <v>1054</v>
       </c>
       <c r="I15" t="n">
         <v>1036.933204946412</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.72</v>
+        <v>-4.36</v>
       </c>
       <c r="L15" t="n">
-        <v>2.51</v>
+        <v>5.45</v>
       </c>
       <c r="M15" t="n">
         <v>0.93</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H16" t="n">
-        <v>1007.8</v>
+        <v>928.9</v>
       </c>
       <c r="I16" t="n">
         <v>1004.75030732261</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.38</v>
+        <v>-11.87</v>
       </c>
       <c r="L16" t="n">
-        <v>7.13</v>
+        <v>12.54</v>
       </c>
       <c r="M16" t="n">
         <v>0.89</v>
       </c>
       <c r="N16" t="n">
-        <v>2.97</v>
+        <v>7.83</v>
       </c>
       <c r="O16" t="n">
         <v>3.61</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>17.33</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H17" t="n">
-        <v>908.75</v>
+        <v>947.1</v>
       </c>
       <c r="I17" t="n">
         <v>937.261249823232</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K17" t="n">
-        <v>2.17</v>
+        <v>-1.96</v>
       </c>
       <c r="L17" t="n">
         <v>9.84</v>
@@ -1410,7 +1613,7 @@
         <v>1.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>4.22</v>
       </c>
       <c r="O17" t="n">
         <v>-7.83</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.22</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="H18" t="n">
-        <v>956.8</v>
+        <v>927.35</v>
       </c>
       <c r="I18" t="n">
         <v>938.467243855014</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K18" t="n">
-        <v>1.02</v>
+        <v>-2.09</v>
       </c>
       <c r="L18" t="n">
         <v>4.45</v>
@@ -1467,7 +1682,7 @@
         <v>3.07</v>
       </c>
       <c r="N18" t="n">
-        <v>2.34</v>
+        <v>3.08</v>
       </c>
       <c r="O18" t="n">
         <v>4.22</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>13</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43333</v>
+        <v>43335</v>
       </c>
       <c r="H19" t="n">
-        <v>784.3</v>
+        <v>788.65</v>
       </c>
       <c r="I19" t="n">
         <v>786.6621027084196</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K19" t="n">
-        <v>15.43</v>
+        <v>14.96</v>
       </c>
       <c r="L19" t="n">
         <v>6.38</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.16</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43353</v>
+        <v>43354</v>
       </c>
       <c r="H20" t="n">
-        <v>744.55</v>
+        <v>727.1</v>
       </c>
       <c r="I20" t="n">
         <v>734.5520885892596</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.59</v>
+        <v>-7.8</v>
       </c>
       <c r="L20" t="n">
-        <v>7.37</v>
+        <v>8.18</v>
       </c>
       <c r="M20" t="n">
         <v>0.25</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>10.26</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43452</v>
+        <v>43453</v>
       </c>
       <c r="H21" t="n">
-        <v>748.1</v>
+        <v>776.45</v>
       </c>
       <c r="I21" t="n">
         <v>750.3403698291675</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.89</v>
+        <v>-6.79</v>
       </c>
       <c r="L21" t="n">
-        <v>4.77</v>
+        <v>9.6</v>
       </c>
       <c r="M21" t="n">
         <v>1.38</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>11.08</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43508</v>
+        <v>43509</v>
       </c>
       <c r="H22" t="n">
-        <v>771.55</v>
+        <v>748.65</v>
       </c>
       <c r="I22" t="n">
         <v>751.5785118768031</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.63</v>
+        <v>-3.58</v>
       </c>
       <c r="L22" t="n">
-        <v>4.08</v>
+        <v>4.53</v>
       </c>
       <c r="M22" t="n">
         <v>0.95</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>13.22</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H23" t="n">
-        <v>779.95</v>
+        <v>804.75</v>
       </c>
       <c r="I23" t="n">
         <v>799.6386191759334</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.18</v>
+        <v>-7.49</v>
       </c>
       <c r="L23" t="n">
-        <v>6.73</v>
+        <v>8.07</v>
       </c>
       <c r="M23" t="n">
         <v>0.63</v>
       </c>
       <c r="N23" t="n">
-        <v>2.31</v>
+        <v>3.18</v>
       </c>
       <c r="O23" t="n">
         <v>-2.97</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>10.14</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H24" t="n">
-        <v>854.75</v>
+        <v>829.65</v>
       </c>
       <c r="I24" t="n">
         <v>847.6256322621382</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K24" t="n">
-        <v>6.21</v>
+        <v>3.09</v>
       </c>
       <c r="L24" t="n">
         <v>3.62</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="N24" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="O24" t="n">
         <v>3.18</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>9.17</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H25" t="n">
-        <v>857.75</v>
+        <v>908.15</v>
       </c>
       <c r="I25" t="n">
         <v>877.0598855542504</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.39</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>4.55</v>
+        <v>9.94</v>
       </c>
       <c r="M25" t="n">
-        <v>0.76</v>
+        <v>1.33</v>
       </c>
       <c r="N25" t="n">
-        <v>5.19</v>
+        <v>5.88</v>
       </c>
       <c r="O25" t="n">
         <v>-2.94</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.76</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H26" t="n">
-        <v>959.55</v>
+        <v>950.25</v>
       </c>
       <c r="I26" t="n">
         <v>951.9705679810833</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K26" t="n">
-        <v>5.66</v>
+        <v>4.64</v>
       </c>
       <c r="L26" t="n">
         <v>4.29</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43714</v>
+        <v>43717</v>
       </c>
       <c r="H27" t="n">
-        <v>905.2</v>
+        <v>928.9</v>
       </c>
       <c r="I27" t="n">
         <v>923.085556029576</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K27" t="n">
-        <v>4.74</v>
+        <v>2.25</v>
       </c>
       <c r="L27" t="n">
         <v>2.89</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.46</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43784</v>
+        <v>43787</v>
       </c>
       <c r="H28" t="n">
-        <v>1200.45</v>
+        <v>1184.3</v>
       </c>
       <c r="I28" t="n">
         <v>1190.462922491246</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K28" t="n">
-        <v>29.23</v>
+        <v>27.49</v>
       </c>
       <c r="L28" t="n">
         <v>3.15</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43846</v>
+        <v>43847</v>
       </c>
       <c r="H29" t="n">
-        <v>1169.7</v>
+        <v>1209.75</v>
       </c>
       <c r="I29" t="n">
         <v>1192.447586794583</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K29" t="n">
-        <v>1.23</v>
+        <v>-2.15</v>
       </c>
       <c r="L29" t="n">
         <v>2.79</v>
@@ -2094,7 +2441,7 @@
         <v>2.46</v>
       </c>
       <c r="N29" t="n">
-        <v>2.46</v>
+        <v>3.42</v>
       </c>
       <c r="O29" t="n">
         <v>-1.35</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>7.54</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H30" t="n">
-        <v>1150.15</v>
+        <v>1142.9</v>
       </c>
       <c r="I30" t="n">
         <v>1147.14991069457</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.93</v>
+        <v>-5.53</v>
       </c>
       <c r="L30" t="n">
-        <v>6.15</v>
+        <v>6.66</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.56</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44015</v>
+        <v>44018</v>
       </c>
       <c r="H31" t="n">
-        <v>875.45</v>
+        <v>885.45</v>
       </c>
       <c r="I31" t="n">
         <v>877.7303890351649</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K31" t="n">
-        <v>23.4</v>
+        <v>22.53</v>
       </c>
       <c r="L31" t="n">
         <v>1.6</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>6</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>8.77</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H32" t="n">
-        <v>1408.55</v>
+        <v>1317.7</v>
       </c>
       <c r="I32" t="n">
         <v>1349.092909389693</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K32" t="n">
-        <v>59.08</v>
+        <v>48.82</v>
       </c>
       <c r="L32" t="n">
         <v>3.81</v>
       </c>
       <c r="M32" t="n">
-        <v>1.46</v>
+        <v>2.16</v>
       </c>
       <c r="N32" t="n">
-        <v>5.02</v>
+        <v>6.45</v>
       </c>
       <c r="O32" t="n">
         <v>1.14</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>193</v>
+        <v>194</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>10</v>
+      </c>
+      <c r="U32" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>13.41</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44326</v>
+        <v>44327</v>
       </c>
       <c r="H33" t="n">
-        <v>1434.45</v>
+        <v>1484.5</v>
       </c>
       <c r="I33" t="n">
         <v>1478.13383899573</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.859999999999999</v>
+        <v>-12.66</v>
       </c>
       <c r="L33" t="n">
-        <v>10.89</v>
+        <v>13.54</v>
       </c>
       <c r="M33" t="n">
         <v>2.03</v>
       </c>
       <c r="N33" t="n">
-        <v>2.64</v>
+        <v>3.49</v>
       </c>
       <c r="O33" t="n">
         <v>-6.45</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.24</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H34" t="n">
-        <v>1503.3</v>
+        <v>1481.2</v>
       </c>
       <c r="I34" t="n">
         <v>1492.857966107156</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K34" t="n">
-        <v>1.27</v>
+        <v>-0.22</v>
       </c>
       <c r="L34" t="n">
         <v>4.33</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>6.87</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44412</v>
+        <v>44413</v>
       </c>
       <c r="H35" t="n">
-        <v>1556.6</v>
+        <v>1570.55</v>
       </c>
       <c r="I35" t="n">
         <v>1565.532759516635</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.09</v>
+        <v>-6.03</v>
       </c>
       <c r="L35" t="n">
-        <v>5.54</v>
+        <v>6.41</v>
       </c>
       <c r="M35" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="N35" t="n">
         <v>2.54</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.88</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44462</v>
+        <v>44463</v>
       </c>
       <c r="H36" t="n">
-        <v>1647.55</v>
+        <v>1615.2</v>
       </c>
       <c r="I36" t="n">
         <v>1624.21388011172</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K36" t="n">
-        <v>4.9</v>
+        <v>2.84</v>
       </c>
       <c r="L36" t="n">
         <v>4.44</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.81</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44480</v>
+        <v>44481</v>
       </c>
       <c r="H37" t="n">
-        <v>1703.95</v>
+        <v>1726.15</v>
       </c>
       <c r="I37" t="n">
         <v>1716.477277199041</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.49</v>
+        <v>-6.87</v>
       </c>
       <c r="L37" t="n">
-        <v>7.29</v>
+        <v>7.77</v>
       </c>
       <c r="M37" t="n">
         <v>1.21</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>7.43</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44524</v>
+        <v>44525</v>
       </c>
       <c r="H38" t="n">
-        <v>1734.15</v>
+        <v>1641.55</v>
       </c>
       <c r="I38" t="n">
         <v>1692.029939353166</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K38" t="n">
-        <v>0.46</v>
+        <v>-4.9</v>
       </c>
       <c r="L38" t="n">
-        <v>7.2</v>
+        <v>7.32</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3</v>
+        <v>2.04</v>
       </c>
       <c r="N38" t="n">
-        <v>4.37</v>
+        <v>5.34</v>
       </c>
       <c r="O38" t="n">
         <v>1.3</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>11.87</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44539</v>
+        <v>44540</v>
       </c>
       <c r="H39" t="n">
-        <v>1730.5</v>
+        <v>1862.85</v>
       </c>
       <c r="I39" t="n">
         <v>1799.093093621756</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.42</v>
+        <v>-13.48</v>
       </c>
       <c r="L39" t="n">
-        <v>5.9</v>
+        <v>14.62</v>
       </c>
       <c r="M39" t="n">
         <v>1.02</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>7.65</v>
       </c>
       <c r="O39" t="n">
         <v>-5.34</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>13.19</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H40" t="n">
-        <v>1785.6</v>
+        <v>1699.4</v>
       </c>
       <c r="I40" t="n">
         <v>1715.943713163159</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.15</v>
+        <v>-8.77</v>
       </c>
       <c r="L40" t="n">
-        <v>8.23</v>
+        <v>10.22</v>
       </c>
       <c r="M40" t="n">
         <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.72</v>
+        <v>4.83</v>
       </c>
       <c r="O40" t="n">
         <v>7.65</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>12.74</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44658</v>
+        <v>44659</v>
       </c>
       <c r="H41" t="n">
-        <v>1882.1</v>
+        <v>1918.65</v>
       </c>
       <c r="I41" t="n">
         <v>1882.310286453549</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K41" t="n">
-        <v>-10.75</v>
+        <v>-12.9</v>
       </c>
       <c r="L41" t="n">
-        <v>12.52</v>
+        <v>13.37</v>
       </c>
       <c r="M41" t="n">
         <v>3.39</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.97</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H42" t="n">
-        <v>1782.4</v>
+        <v>1722.95</v>
       </c>
       <c r="I42" t="n">
         <v>1771.47190316451</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>-7.1</v>
+        <v>-10.2</v>
       </c>
       <c r="L42" t="n">
-        <v>7.49</v>
+        <v>10.66</v>
       </c>
       <c r="M42" t="n">
         <v>0.63</v>
       </c>
       <c r="N42" t="n">
-        <v>2.54</v>
+        <v>3.34</v>
       </c>
       <c r="O42" t="n">
         <v>1.94</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44704</v>
+        <v>44705</v>
       </c>
       <c r="H43" t="n">
-        <v>1802.1</v>
+        <v>1828.95</v>
       </c>
       <c r="I43" t="n">
         <v>1825.693863999558</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.59</v>
+        <v>-6.15</v>
       </c>
       <c r="L43" t="n">
-        <v>6.86</v>
+        <v>7.04</v>
       </c>
       <c r="M43" t="n">
         <v>1.74</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H44" t="n">
-        <v>2223.9</v>
+        <v>2174.5</v>
       </c>
       <c r="I44" t="n">
         <v>2179.782871143887</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K44" t="n">
-        <v>21.59</v>
+        <v>18.89</v>
       </c>
       <c r="L44" t="n">
         <v>6.25</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44868</v>
+        <v>44869</v>
       </c>
       <c r="H45" t="n">
-        <v>2202.8</v>
+        <v>2265</v>
       </c>
       <c r="I45" t="n">
         <v>2246.574093190823</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.3</v>
+        <v>-4.16</v>
       </c>
       <c r="L45" t="n">
-        <v>4.05</v>
+        <v>4.62</v>
       </c>
       <c r="M45" t="n">
         <v>1.89</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.64</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44890</v>
+        <v>44893</v>
       </c>
       <c r="H46" t="n">
-        <v>2116.7</v>
+        <v>2106.15</v>
       </c>
       <c r="I46" t="n">
         <v>2107.282564333213</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.55</v>
+        <v>-7.01</v>
       </c>
       <c r="L46" t="n">
         <v>9.470000000000001</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.17</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44902</v>
+        <v>44903</v>
       </c>
       <c r="H47" t="n">
-        <v>2213.3</v>
+        <v>2244.15</v>
       </c>
       <c r="I47" t="n">
         <v>2231.877403008002</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.09</v>
+        <v>-6.55</v>
       </c>
       <c r="L47" t="n">
-        <v>6.63</v>
+        <v>6.99</v>
       </c>
       <c r="M47" t="n">
         <v>2.11</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>7.87</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H48" t="n">
-        <v>2179.55</v>
+        <v>2123.3</v>
       </c>
       <c r="I48" t="n">
         <v>2127.336168093024</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.88</v>
+        <v>-5.39</v>
       </c>
       <c r="L48" t="n">
-        <v>3.35</v>
+        <v>5.85</v>
       </c>
       <c r="M48" t="n">
         <v>0.66</v>
       </c>
       <c r="N48" t="n">
-        <v>2.41</v>
+        <v>2.58</v>
       </c>
       <c r="O48" t="n">
         <v>1.39</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>9.48</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44943</v>
+        <v>44944</v>
       </c>
       <c r="H49" t="n">
-        <v>2243.85</v>
+        <v>2334.65</v>
       </c>
       <c r="I49" t="n">
         <v>2293.24724179062</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.68</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>9.57</v>
+        <v>10.66</v>
       </c>
       <c r="M49" t="n">
         <v>2.91</v>
       </c>
       <c r="N49" t="n">
-        <v>2.83</v>
+        <v>4.05</v>
       </c>
       <c r="O49" t="n">
         <v>-2.58</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45065</v>
+        <v>45068</v>
       </c>
       <c r="H50" t="n">
-        <v>2835.95</v>
+        <v>2589.9</v>
       </c>
       <c r="I50" t="n">
         <v>2765.07608294792</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K50" t="n">
-        <v>21.47</v>
+        <v>10.93</v>
       </c>
       <c r="L50" t="n">
         <v>5.65</v>
       </c>
       <c r="M50" t="n">
-        <v>1.19</v>
+        <v>3.29</v>
       </c>
       <c r="N50" t="n">
-        <v>3.84</v>
+        <v>8.68</v>
       </c>
       <c r="O50" t="n">
         <v>4.05</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>13.49</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45092</v>
+        <v>45093</v>
       </c>
       <c r="H51" t="n">
-        <v>2858.05</v>
+        <v>2889.6</v>
       </c>
       <c r="I51" t="n">
         <v>2877.754331977869</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>-10.35</v>
+        <v>-11.57</v>
       </c>
       <c r="L51" t="n">
-        <v>11.13</v>
+        <v>11.75</v>
       </c>
       <c r="M51" t="n">
         <v>0.87</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.3</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45127</v>
+        <v>45128</v>
       </c>
       <c r="H52" t="n">
-        <v>2769.45</v>
+        <v>2753.1</v>
       </c>
       <c r="I52" t="n">
         <v>2753.906753911615</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.16</v>
+        <v>-4.72</v>
       </c>
       <c r="L52" t="n">
         <v>7.45</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.91</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45135</v>
+        <v>45138</v>
       </c>
       <c r="H53" t="n">
-        <v>2938.8</v>
+        <v>3034.25</v>
       </c>
       <c r="I53" t="n">
         <v>2970.874432321847</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>-6.75</v>
+        <v>-10.21</v>
       </c>
       <c r="L53" t="n">
-        <v>6.93</v>
+        <v>12.59</v>
       </c>
       <c r="M53" t="n">
-        <v>0.35</v>
+        <v>2.12</v>
       </c>
       <c r="N53" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="O53" t="n">
         <v>-0.59</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>7.55</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45147</v>
+        <v>45148</v>
       </c>
       <c r="H54" t="n">
-        <v>2843.1</v>
+        <v>2794.65</v>
       </c>
       <c r="I54" t="n">
         <v>2805.156871837446</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.3</v>
+        <v>-7.9</v>
       </c>
       <c r="L54" t="n">
-        <v>7.64</v>
+        <v>8.25</v>
       </c>
       <c r="M54" t="n">
         <v>0.03</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45168</v>
+        <v>45169</v>
       </c>
       <c r="H55" t="n">
-        <v>2945.75</v>
+        <v>2987.85</v>
       </c>
       <c r="I55" t="n">
         <v>2953.418989381849</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.41</v>
+        <v>-6.91</v>
       </c>
       <c r="L55" t="n">
-        <v>6.04</v>
+        <v>8.85</v>
       </c>
       <c r="M55" t="n">
         <v>0.74</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>6.43</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45189</v>
+        <v>45190</v>
       </c>
       <c r="H56" t="n">
-        <v>2875.1</v>
+        <v>2849.15</v>
       </c>
       <c r="I56" t="n">
         <v>2859.099289609733</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.77</v>
+        <v>-4.64</v>
       </c>
       <c r="L56" t="n">
-        <v>4.4</v>
+        <v>5.08</v>
       </c>
       <c r="M56" t="n">
         <v>0.13</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.74</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="H57" t="n">
-        <v>2685.35</v>
+        <v>2720.2</v>
       </c>
       <c r="I57" t="n">
         <v>2696.024079753908</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K57" t="n">
-        <v>5.75</v>
+        <v>4.53</v>
       </c>
       <c r="L57" t="n">
         <v>2.08</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.76</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H58" t="n">
-        <v>5541.35</v>
+        <v>4854.3</v>
       </c>
       <c r="I58" t="n">
         <v>5087.947598037559</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K58" t="n">
-        <v>103.71</v>
+        <v>78.45</v>
       </c>
       <c r="L58" t="n">
         <v>1.92</v>
@@ -3747,7 +4442,7 @@
         <v>1.36</v>
       </c>
       <c r="N58" t="n">
-        <v>4.02</v>
+        <v>12.4</v>
       </c>
       <c r="O58" t="n">
         <v>1.3</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>8</v>
+      </c>
+      <c r="U58" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>18.65</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H59" t="n">
-        <v>5634.75</v>
+        <v>5934.6</v>
       </c>
       <c r="I59" t="n">
         <v>5648.988607892821</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K59" t="n">
-        <v>-16.08</v>
+        <v>-22.25</v>
       </c>
       <c r="L59" t="n">
-        <v>17.2</v>
+        <v>24.18</v>
       </c>
       <c r="M59" t="n">
         <v>3.89</v>
       </c>
       <c r="N59" t="n">
-        <v>4.69</v>
+        <v>5.32</v>
       </c>
       <c r="O59" t="n">
         <v>-12.4</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>13.98</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45489</v>
+        <v>45491</v>
       </c>
       <c r="H60" t="n">
-        <v>5689.6</v>
+        <v>5424.95</v>
       </c>
       <c r="I60" t="n">
         <v>5471.941275833453</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.13</v>
+        <v>-8.59</v>
       </c>
       <c r="L60" t="n">
-        <v>5.63</v>
+        <v>9.44</v>
       </c>
       <c r="M60" t="n">
         <v>0.16</v>
       </c>
       <c r="N60" t="n">
-        <v>2.46</v>
+        <v>4.65</v>
       </c>
       <c r="O60" t="n">
         <v>5.32</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>11.98</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45558</v>
+        <v>45559</v>
       </c>
       <c r="H61" t="n">
-        <v>5285.7</v>
+        <v>5405.5</v>
       </c>
       <c r="I61" t="n">
         <v>5325.503344941371</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K61" t="n">
-        <v>2.57</v>
+        <v>0.36</v>
       </c>
       <c r="L61" t="n">
         <v>5.02</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.02</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H62" t="n">
-        <v>5699.5</v>
+        <v>5514.45</v>
       </c>
       <c r="I62" t="n">
         <v>5586.424142706386</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K62" t="n">
-        <v>5.44</v>
+        <v>2.02</v>
       </c>
       <c r="L62" t="n">
         <v>2.33</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>12.18</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="H63" t="n">
-        <v>5217.85</v>
+        <v>5598.1</v>
       </c>
       <c r="I63" t="n">
         <v>5515.621316357952</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K63" t="n">
-        <v>5.38</v>
+        <v>-1.52</v>
       </c>
       <c r="L63" t="n">
         <v>3.36</v>
       </c>
       <c r="M63" t="n">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="N63" t="n">
-        <v>3.13</v>
+        <v>7.29</v>
       </c>
       <c r="O63" t="n">
         <v>-3.25</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>12.4</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H64" t="n">
-        <v>5814.15</v>
+        <v>5232.75</v>
       </c>
       <c r="I64" t="n">
         <v>5655.42786677626</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K64" t="n">
-        <v>3.86</v>
+        <v>-6.53</v>
       </c>
       <c r="L64" t="n">
-        <v>5.13</v>
+        <v>7.17</v>
       </c>
       <c r="M64" t="n">
         <v>1.53</v>
       </c>
       <c r="N64" t="n">
-        <v>2.24</v>
+        <v>10</v>
       </c>
       <c r="O64" t="n">
         <v>7.29</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>17.13</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="H65" t="n">
-        <v>3899.75</v>
+        <v>4127.6</v>
       </c>
       <c r="I65" t="n">
         <v>3996.291612206745</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K65" t="n">
-        <v>25.47</v>
+        <v>21.12</v>
       </c>
       <c r="L65" t="n">
         <v>12.29</v>
       </c>
       <c r="M65" t="n">
-        <v>2.52</v>
+        <v>3.53</v>
       </c>
       <c r="N65" t="n">
-        <v>4.61</v>
+        <v>5.84</v>
       </c>
       <c r="O65" t="n">
         <v>-10</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>11.86</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H66" t="n">
-        <v>3754.25</v>
+        <v>2812.45</v>
       </c>
       <c r="I66" t="n">
         <v>3657.693396299728</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K66" t="n">
-        <v>-9.050000000000001</v>
+        <v>-31.86</v>
       </c>
       <c r="L66" t="n">
-        <v>10.47</v>
+        <v>40.64</v>
       </c>
       <c r="M66" t="n">
-        <v>1.55</v>
+        <v>34.74</v>
       </c>
       <c r="N66" t="n">
-        <v>6.11</v>
+        <v>25.09</v>
       </c>
       <c r="O66" t="n">
         <v>5.84</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>27.1</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45797</v>
+        <v>45798</v>
       </c>
       <c r="H67" t="n">
-        <v>3127.7</v>
+        <v>3290.8</v>
       </c>
       <c r="I67" t="n">
         <v>3185.855227161011</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K67" t="n">
-        <v>-11.21</v>
+        <v>-17.01</v>
       </c>
       <c r="L67" t="n">
-        <v>14.06</v>
+        <v>17.51</v>
       </c>
       <c r="M67" t="n">
         <v>4.48</v>
       </c>
       <c r="N67" t="n">
-        <v>4.09</v>
+        <v>5.21</v>
       </c>
       <c r="O67" t="n">
         <v>-25.09</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>13.14</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45828</v>
+        <v>45831</v>
       </c>
       <c r="H68" t="n">
-        <v>3214.2</v>
+        <v>3091.6</v>
       </c>
       <c r="I68" t="n">
         <v>3139.793747447751</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.33</v>
+        <v>-6.05</v>
       </c>
       <c r="L68" t="n">
-        <v>4.93</v>
+        <v>6.34</v>
       </c>
       <c r="M68" t="n">
         <v>2.22</v>
       </c>
       <c r="N68" t="n">
-        <v>2.5</v>
+        <v>3.81</v>
       </c>
       <c r="O68" t="n">
         <v>5.21</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>10.61</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="H69" t="n">
-        <v>3155.1</v>
+        <v>3197.2</v>
       </c>
       <c r="I69" t="n">
         <v>3176.215099081617</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.05</v>
+        <v>-3.42</v>
       </c>
       <c r="L69" t="n">
         <v>9.289999999999999</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.85</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H70" t="n">
-        <v>3156.3</v>
+        <v>3096.3</v>
       </c>
       <c r="I70" t="n">
         <v>3115.159833841889</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.28</v>
+        <v>-3.16</v>
       </c>
       <c r="L70" t="n">
         <v>5.62</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>7.49</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="H71" t="n">
-        <v>3084.2</v>
+        <v>3232.6</v>
       </c>
       <c r="I71" t="n">
         <v>3221.937867621387</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K71" t="n">
-        <v>0.39</v>
+        <v>-4.4</v>
       </c>
       <c r="L71" t="n">
         <v>5.83</v>
@@ -4488,7 +5339,7 @@
         <v>1.03</v>
       </c>
       <c r="N71" t="n">
-        <v>2.77</v>
+        <v>4.81</v>
       </c>
       <c r="O71" t="n">
         <v>-1.9</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.65</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="H72" t="n">
-        <v>3204.2</v>
+        <v>3142.8</v>
       </c>
       <c r="I72" t="n">
         <v>3147.299576760452</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.88</v>
+        <v>-2.78</v>
       </c>
       <c r="L72" t="n">
         <v>4.31</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="H73" t="n">
-        <v>3096.3</v>
+        <v>3101.3</v>
       </c>
       <c r="I73" t="n">
         <v>3098.534040615151</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K73" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="L73" t="n">
         <v>2.14</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H74" t="n">
-        <v>3129.6</v>
+        <v>2988.3</v>
       </c>
       <c r="I74" t="n">
         <v>3042.125586468041</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K74" t="n">
-        <v>0.91</v>
+        <v>-3.64</v>
       </c>
       <c r="L74" t="n">
         <v>6.77</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>13.78</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H75" t="n">
-        <v>3222.5</v>
+        <v>3388.5</v>
       </c>
       <c r="I75" t="n">
         <v>3332.213331998368</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K75" t="n">
-        <v>-7.84</v>
+        <v>-13.39</v>
       </c>
       <c r="L75" t="n">
-        <v>8.92</v>
+        <v>13.86</v>
       </c>
       <c r="M75" t="n">
         <v>3.4</v>
       </c>
       <c r="N75" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="O75" t="n">
         <v>-4.51</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>13.14</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H76" t="n">
-        <v>3571.6</v>
+        <v>3495</v>
       </c>
       <c r="I76" t="n">
         <v>3520.597676369965</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K76" t="n">
-        <v>5.4</v>
+        <v>3.14</v>
       </c>
       <c r="L76" t="n">
         <v>4.62</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="H77" t="n">
-        <v>3658.8</v>
+        <v>3760</v>
       </c>
       <c r="I77" t="n">
         <v>3737.96966549909</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K77" t="n">
-        <v>-4.69</v>
+        <v>-7.58</v>
       </c>
       <c r="L77" t="n">
         <v>10.3</v>
@@ -4830,7 +5753,7 @@
         <v>0.85</v>
       </c>
       <c r="N77" t="n">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="O77" t="n">
         <v>-2.14</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>8.56</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H78" t="n">
-        <v>3957</v>
+        <v>3770</v>
       </c>
       <c r="I78" t="n">
         <v>3800.860130610769</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K78" t="n">
-        <v>5.24</v>
+        <v>0.27</v>
       </c>
       <c r="L78" t="n">
         <v>2.6</v>
@@ -4887,7 +5822,7 @@
         <v>1.07</v>
       </c>
       <c r="N78" t="n">
-        <v>1.47</v>
+        <v>4.73</v>
       </c>
       <c r="O78" t="n">
         <v>2.77</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>30</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.8</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121.8</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -9965,7 +10920,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -9975,7 +10930,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -9985,7 +10940,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42.9</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="14">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.14</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.02</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.85</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>103.71</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.2</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.62</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="21">
@@ -10065,7 +11020,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.2</v>
+        <v>40.64</v>
       </c>
     </row>
     <row r="22">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.55</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="25">
@@ -10105,7 +11060,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.27</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="26">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.54</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="27">
@@ -10125,7 +11080,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.22</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="28">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
